--- a/Luban/Config/Datas/#BattleVariantConfig.xlsx
+++ b/Luban/Config/Datas/#BattleVariantConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFC5DD5-B503-4BED-813E-9E419C7B70E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F11070-84C9-44F3-83E1-895B1DE18E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,118 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ParamEx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,183 +172,284 @@
     <t>爆血</t>
   </si>
   <si>
+    <t>与杀式交锋时只会被威力大于125的招式破招，随机减少一个键</t>
+  </si>
+  <si>
+    <t>与杀式交锋时只会被威力超过了15的百分比的招式破招，随机减少一个键</t>
+  </si>
+  <si>
+    <t>与杀式交锋时只会被威力大于140的招式破招，随机减少一个键</t>
+  </si>
+  <si>
+    <t>释放成功下个回合玄炁的自然恢复增加5，行动后获得过劲状态</t>
+  </si>
+  <si>
+    <t>释放成功下个回合刚炁的自然恢复增加5，行动后获得过劲状态</t>
+  </si>
+  <si>
+    <t>VariantScript</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次的行动延迟1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次的行动延迟2息，炁的消耗减少20%（至多10），行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次的行动延迟2息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次的行动延迟2息，前2息内若成为目标的杀式目标则立即行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动期间破额外增加60+GR*6，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动期间防额外增加60+GR*6，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动决定后获得30+GR*3层护体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>招式的威力增加5的百分比，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炁拶类招式施加的状态层数增加50%（至少1）（只作用一个单位，优先行动目标再者自身），行动的消耗不会低于基础消耗，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>行动所选对手本次行动速低于自身则该对手本次杀式行动目标转来至自身，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>释放成功下个回合玄炁的自然恢复增加3，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>释放成功下个回合刚炁的自然恢复增加3，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5002</t>
+  </si>
+  <si>
+    <t>5003</t>
+  </si>
+  <si>
+    <t>5004</t>
+  </si>
+  <si>
+    <t>5005</t>
+  </si>
+  <si>
+    <t>5006</t>
+  </si>
+  <si>
+    <t>5007</t>
+  </si>
+  <si>
+    <t>5008</t>
+  </si>
+  <si>
+    <t>5009</t>
+  </si>
+  <si>
+    <t>5010</t>
+  </si>
+  <si>
+    <t>5011</t>
+  </si>
+  <si>
+    <t>5012</t>
+  </si>
+  <si>
+    <t>5013</t>
+  </si>
+  <si>
+    <t>5014</t>
+  </si>
+  <si>
+    <t>5015</t>
+  </si>
+  <si>
+    <t>5016</t>
+  </si>
+  <si>
+    <t>5017</t>
+  </si>
+  <si>
+    <t>5018</t>
+  </si>
+  <si>
+    <t>5019</t>
+  </si>
+  <si>
+    <t>5020</t>
+  </si>
+  <si>
+    <t>5021</t>
+  </si>
+  <si>
+    <t>5022</t>
+  </si>
+  <si>
+    <t>5023</t>
+  </si>
+  <si>
+    <t>5024</t>
+  </si>
+  <si>
+    <t>5025</t>
+  </si>
+  <si>
+    <t>5026</t>
+  </si>
+  <si>
+    <t>5027</t>
+  </si>
+  <si>
+    <t>5028</t>
+  </si>
+  <si>
+    <t>5011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀式行动决定后受到目标外敌手的杀式攻击时将其变为本次行动目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交锋时减少目标本次杀式行动所能造成的伤害，减少量为本次杀式的威力*力50%，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>与杀式交锋时只会被威力超过了10的百分比的招式破招，随机减少一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>与杀式交锋时只会被威力大于125的招式破招，随机减少一个键</t>
-  </si>
-  <si>
-    <t>与杀式交锋时只会被威力超过了15的百分比的招式破招，随机减少一个键</t>
-  </si>
-  <si>
-    <t>与杀式交锋时只会被威力大于140的招式破招，随机减少一个键</t>
-  </si>
-  <si>
-    <t>释放成功下个回合玄炁的自然恢复增加5，行动后获得过劲状态</t>
-  </si>
-  <si>
-    <t>释放成功下个回合刚炁的自然恢复增加5，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleVariant5001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleVariant5002</t>
+  </si>
+  <si>
+    <t>BattleVariant5003</t>
+  </si>
+  <si>
+    <t>BattleVariant5004</t>
+  </si>
+  <si>
+    <t>BattleVariant5005</t>
+  </si>
+  <si>
+    <t>BattleVariant5006</t>
+  </si>
+  <si>
+    <t>BattleVariant5007</t>
+  </si>
+  <si>
+    <t>BattleVariant5008</t>
+  </si>
+  <si>
+    <t>BattleVariant5009</t>
+  </si>
+  <si>
+    <t>BattleVariant5010</t>
+  </si>
+  <si>
+    <t>BattleVariant5011</t>
+  </si>
+  <si>
+    <t>BattleVariant5012</t>
+  </si>
+  <si>
+    <t>BattleVariant5013</t>
+  </si>
+  <si>
+    <t>BattleVariant5014</t>
+  </si>
+  <si>
+    <t>BattleVariant5015</t>
+  </si>
+  <si>
+    <t>BattleVariant5016</t>
+  </si>
+  <si>
+    <t>BattleVariant5017</t>
+  </si>
+  <si>
+    <t>BattleVariant5018</t>
+  </si>
+  <si>
+    <t>BattleVariant5019</t>
+  </si>
+  <si>
+    <t>BattleVariant5020</t>
+  </si>
+  <si>
+    <t>BattleVariant5021</t>
+  </si>
+  <si>
+    <t>BattleVariant5022</t>
+  </si>
+  <si>
+    <t>BattleVariant5023</t>
+  </si>
+  <si>
+    <t>BattleVariant5024</t>
+  </si>
+  <si>
+    <t>BattleVariant5025</t>
+  </si>
+  <si>
+    <t>BattleVariant5026</t>
+  </si>
+  <si>
+    <t>BattleVariant5027</t>
+  </si>
+  <si>
+    <t>BattleVariant5028</t>
   </si>
   <si>
     <t>行动决定后获得9+GR*9层护体，行动后获得过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>根据目标的卦位至多使本次的行动加快4息，获得2层过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>根据目标的卦位至多使目标本次的行动延迟4息，获得2层过劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>招式的威力减少10的百分比，随机获得1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>本次的行动加快1息，行动后获得1层缓速状态</t>
-  </si>
-  <si>
-    <t>VariantScript</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleVariant1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleVariant1002</t>
-  </si>
-  <si>
-    <t>BattleVariant1012</t>
-  </si>
-  <si>
-    <t>BattleVariant1021</t>
-  </si>
-  <si>
-    <t>BattleVariant1022</t>
-  </si>
-  <si>
-    <t>BattleVariant1003</t>
-  </si>
-  <si>
-    <t>BattleVariant1004</t>
-  </si>
-  <si>
-    <t>BattleVariant1005</t>
-  </si>
-  <si>
-    <t>BattleVariant1006</t>
-  </si>
-  <si>
-    <t>BattleVariant1007</t>
-  </si>
-  <si>
-    <t>BattleVariant1008</t>
-  </si>
-  <si>
-    <t>BattleVariant1009</t>
-  </si>
-  <si>
-    <t>BattleVariant1010</t>
-  </si>
-  <si>
-    <t>BattleVariant1011</t>
-  </si>
-  <si>
-    <t>BattleVariant1013</t>
-  </si>
-  <si>
-    <t>BattleVariant1014</t>
-  </si>
-  <si>
-    <t>BattleVariant1015</t>
-  </si>
-  <si>
-    <t>BattleVariant1016</t>
-  </si>
-  <si>
-    <t>BattleVariant1017</t>
-  </si>
-  <si>
-    <t>BattleVariant1018</t>
-  </si>
-  <si>
-    <t>BattleVariant1019</t>
-  </si>
-  <si>
-    <t>BattleVariant1020</t>
-  </si>
-  <si>
-    <t>BattleVariant1023</t>
-  </si>
-  <si>
-    <t>BattleVariant1024</t>
-  </si>
-  <si>
-    <t>BattleVariant1025</t>
-  </si>
-  <si>
-    <t>BattleVariant1026</t>
-  </si>
-  <si>
-    <t>BattleVariant1027</t>
-  </si>
-  <si>
-    <t>BattleVariant1028</t>
-  </si>
-  <si>
-    <t>本次的行动延迟1息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次的行动延迟2息，炁的消耗减少20%（至多10），行动后获得过劲状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次的行动延迟2息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次的行动延迟2息，前2息内若成为目标的杀式目标则立即行动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动期间破额外增加60+GR*6，行动后获得过劲状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动期间防额外增加60+GR*6，行动后获得过劲状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动决定后获得30+GR*3层护体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招式的威力增加5的百分比，行动后获得过劲状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炁拶类招式施加的状态层数增加50%（至少1）（只作用一个单位，优先行动目标再者自身），行动的消耗不会低于基础消耗，行动后获得过劲状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,10 +848,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -882,7 +871,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -899,486 +888,486 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
